--- a/figs/Supp_Table4_References/output/SuppTable4_references.xlsx
+++ b/figs/Supp_Table4_References/output/SuppTable4_references.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="References" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -556,7 +556,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Source: figs/Supp_Table4_References/output/SuppTable4_reference_sizes.csv (figs/Supp_Table4_References/analysis/supp_table_references.R, which restricts the reference files used for scoring as the scoring scripts do); table made by figs/Supp_Table4_References/analysis/supp_table_references.py on 2026-10-16.</t>
+          <t>Source: figs/Supp_Table4_References/output/SuppTable4_reference_sizes.csv (figs/Supp_Table4_References/analysis/supp_table_references.R, which restricts the reference files used for scoring as the scoring scripts do); table made by figs/Supp_Table4_References/analysis/supp_table_references.py on 2026-10-17.</t>
         </is>
       </c>
     </row>

--- a/figs/Supp_Table4_References/output/SuppTable4_references.xlsx
+++ b/figs/Supp_Table4_References/output/SuppTable4_references.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="References" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -511,7 +511,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Samples — the numbers of mice or samples in the first and second groups, whose counts were summed per group.</t>
+          <t>Samples — the numbers of mice, donors or samples in the first and second groups, whose counts were summed per group.</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Genes in the reference: up / down — number of genes in the up- and down-regulated lists (gene sets: the number of mouse genes in the set) before the restriction to the genes analysed.</t>
+          <t>Genes in the reference: up / down — number of genes in the up- and down-regulated lists (gene sets: the number of genes in the set; mouse orthologues for Figs. 2 and 3, human genes for Supplementary Fig. S5) before the restriction to the genes analysed.</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Source: figs/Supp_Table4_References/output/SuppTable4_reference_sizes.csv (figs/Supp_Table4_References/analysis/supp_table_references.R, which restricts the reference files used for scoring as the scoring scripts do); table made by figs/Supp_Table4_References/analysis/supp_table_references.py on 2026-10-17.</t>
+          <t>Source: figs/Supp_Table4_References/output/SuppTable4_reference_sizes.csv (figs/Supp_Table4_References/analysis/supp_table_references.R, which restricts the reference files used for scoring as the scoring scripts do); table made by figs/Supp_Table4_References/analysis/supp_table_references.py on 2026-10-19.</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1262,6 +1262,246 @@
       </c>
       <c r="N11" s="2" t="n"/>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>IFNb</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>A (differential expression list)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Supplementary Fig. S5c, e</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Kang et al., human PBMC (Supplementary Fig. S5)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Galbraith et al., 2022; GEO GSE191317 (raw gene counts; 3′ mRNA-seq)</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Peripheral blood mononuclear cells, IFN-β vs mock (PBS), 18 h</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7 vs 7 donors</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Counts summed per group, converted to CPM over the nuclear genes; genes ranked by the difference in log2(CPM + 1); top 500 per direction, then restricted to the genes analysed; gene names matched to the data of Kang et al. by Ensembl ID</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Genes without informative names, mitochondrial genes and haemoglobin genes</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>5142</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>276</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>PGE2</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>A (differential expression list)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Supplementary Fig. S5c, e</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Kang et al., human PBMC (Supplementary Fig. S5)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Sokhi et al., 2025; GEO GSE272019 (raw gene counts)</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>CD14+ monocytes cultured overnight with M-CSF, PGE2 (280 nM) vs unstimulated, 3 h</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3 vs 3 donors</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Counts summed per group, converted to CPM over the nuclear genes; genes ranked by the difference in log2(CPM + 1); top 500 per direction, then restricted to the genes analysed; gene names matched to the data of Kang et al. by Ensembl ID</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Genes without informative names, mitochondrial genes and haemoglobin genes</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>5142</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>148</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Interferon (human)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>B (gene set)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Supplementary Fig. S5d, f</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Kang et al., human PBMC (Supplementary Fig. S5)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>MSigDB Hallmark INTERFERON_ALPHA_RESPONSE, human genes (msigdbr 26.1.0; MSigDB 2026.1.Hs); gene names matched to the data of Kang et al. by Ensembl ID</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Membership: the whole set, without order or direction</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="4" t="n">
+        <v>5142</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="N14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Chemokine</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>B (gene set)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Supplementary Fig. S5d, f</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Kang et al., human PBMC (Supplementary Fig. S5)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>KEGG CHEMOKINE_SIGNALING_PATHWAY (MSigDB C2, KEGG legacy), human genes (msigdbr 26.1.0; MSigDB 2026.1.Hs); gene names matched to the data of Kang et al. by Ensembl ID</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Membership: the whole set, without order or direction</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>188</v>
+      </c>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="4" t="n">
+        <v>5142</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="N15" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
